--- a/Big 4 Capex and Cloud Growth.xlsx
+++ b/Big 4 Capex and Cloud Growth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerem\OneDrive\Masaüstü\Financial Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C09B0A-4D1A-4E0B-942C-006CD7D65264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF77D34-6AAF-4FCA-A756-838F59E53491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32712" yWindow="312" windowWidth="26448" windowHeight="14052" xr2:uid="{DD181D79-B43F-4101-885F-595C61B85884}"/>
+    <workbookView xWindow="30828" yWindow="492" windowWidth="29364" windowHeight="15768" xr2:uid="{DD181D79-B43F-4101-885F-595C61B85884}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -365,15 +365,15 @@
     <xf numFmtId="16" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8851,6 +8851,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -8944,7 +8945,7 @@
             <c:numRef>
               <c:f>'[1]Ad Sales Charts'!$AC$73:$AK$73</c:f>
               <c:numCache>
-                <c:formatCode>0.0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.41928066037735851</c:v>
@@ -9007,6 +9008,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -9100,7 +9102,7 @@
             <c:numRef>
               <c:f>'[1]Ad Sales Charts'!$AC$74:$AK$74</c:f>
               <c:numCache>
-                <c:formatCode>0.0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.44422169811320755</c:v>
@@ -9167,6 +9169,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="0.00%" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -9260,7 +9263,7 @@
             <c:numRef>
               <c:f>'[1]Ad Sales Charts'!$AC$75:$AK$75</c:f>
               <c:numCache>
-                <c:formatCode>0.0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.13649764150943397</c:v>
@@ -10584,7 +10587,7 @@
             <c:numRef>
               <c:f>'[1]Ad Sales Charts'!$Y$12:$AG$12</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.13036224976167779</c:v>
@@ -10812,7 +10815,7 @@
             <c:numRef>
               <c:f>'[1]Ad Sales Charts'!$Y$13:$AG$13</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.2681043379239173</c:v>
@@ -11015,7 +11018,7 @@
             <c:numRef>
               <c:f>'[1]Ad Sales Charts'!$Y$14:$AG$14</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>0.24345357030181933</c:v>
@@ -18653,7 +18656,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="438" row="8">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="9">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
   <wetp:taskpane dockstate="right" visibility="0" width="438" row="9">
@@ -18729,41 +18732,41 @@
       <c r="L2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="R2" s="22">
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="R2" s="25">
         <v>2023</v>
       </c>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22">
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25">
         <v>2023</v>
       </c>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
-      <c r="Z2" s="22">
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="25">
         <v>2024</v>
       </c>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="22"/>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22">
+      <c r="AA2" s="25"/>
+      <c r="AB2" s="25"/>
+      <c r="AC2" s="25"/>
+      <c r="AD2" s="25">
         <v>2025</v>
       </c>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AG2" s="22"/>
-      <c r="AH2" s="22">
+      <c r="AE2" s="25"/>
+      <c r="AF2" s="25"/>
+      <c r="AG2" s="25"/>
+      <c r="AH2" s="25">
         <v>2026</v>
       </c>
-      <c r="AI2" s="22"/>
-      <c r="AJ2" s="22"/>
-      <c r="AK2" s="22"/>
+      <c r="AI2" s="25"/>
+      <c r="AJ2" s="25"/>
+      <c r="AK2" s="25"/>
       <c r="AZ2" s="20"/>
       <c r="BA2" s="20" t="str" cm="1">
         <f t="array" ref="BA2">LOOKUP(2,1/($V$2:V$2&lt;&gt;""),$V$2:V$2)&amp;" "&amp;V$4</f>
@@ -18817,28 +18820,28 @@
         <f t="array" ref="BM2">LOOKUP(2,1/($V$2:AH$2&lt;&gt;""),$V$2:AH$2)&amp;" "&amp;AH$4</f>
         <v>2026 Q1</v>
       </c>
-      <c r="BN2" s="26" t="s">
+      <c r="BN2" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="BO2" s="26" t="s">
+      <c r="BO2" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="BP2" s="26" t="s">
+      <c r="BP2" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="BQ2" s="26" t="s">
+      <c r="BQ2" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="BR2" s="26" t="s">
+      <c r="BR2" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BS2" s="26" t="s">
+      <c r="BS2" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BT2" s="26" t="s">
+      <c r="BT2" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="BU2" s="26" t="s">
+      <c r="BU2" s="24" t="s">
         <v>49</v>
       </c>
     </row>
@@ -18874,11 +18877,11 @@
         <f>K3*1.25</f>
         <v>268750</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
       <c r="R3" s="19" t="s">
         <v>29</v>
       </c>
@@ -18995,35 +18998,35 @@
         <f t="shared" si="0"/>
         <v>0.28427922233231967</v>
       </c>
-      <c r="BN3" s="24" t="s">
+      <c r="BN3" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="BO3" s="25">
-        <f>AB$10</f>
+      <c r="BO3" s="23">
+        <f t="shared" ref="BO3:BU3" si="1">AB$10</f>
         <v>27452</v>
       </c>
-      <c r="BP3" s="25">
-        <f>AC$10</f>
+      <c r="BP3" s="23">
+        <f t="shared" si="1"/>
         <v>28786</v>
       </c>
-      <c r="BQ3" s="25">
-        <f>AD$10</f>
+      <c r="BQ3" s="23">
+        <f t="shared" si="1"/>
         <v>29267</v>
       </c>
-      <c r="BR3" s="25">
-        <f>AE$10</f>
+      <c r="BR3" s="23">
+        <f t="shared" si="1"/>
         <v>30873</v>
       </c>
-      <c r="BS3" s="25">
-        <f>AF$10</f>
+      <c r="BS3" s="23">
+        <f t="shared" si="1"/>
         <v>33006</v>
       </c>
-      <c r="BT3" s="25">
-        <f>AG$10</f>
+      <c r="BT3" s="23">
+        <f t="shared" si="1"/>
         <v>35579</v>
       </c>
-      <c r="BU3" s="25">
-        <f>AH$10</f>
+      <c r="BU3" s="23">
+        <f t="shared" si="1"/>
         <v>37587</v>
       </c>
     </row>
@@ -19055,11 +19058,11 @@
       <c r="L4" s="8">
         <v>274835</v>
       </c>
-      <c r="M4" s="22" t="s">
+      <c r="M4" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
       <c r="T4" s="10" t="s">
         <v>31</v>
       </c>
@@ -19168,35 +19171,35 @@
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
-      <c r="BN4" s="24" t="s">
+      <c r="BN4" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="BO4" s="25">
-        <f>AB$11</f>
+      <c r="BO4" s="23">
+        <f t="shared" ref="BO4:BU4" si="2">AB$11</f>
         <v>17232</v>
       </c>
-      <c r="BP4" s="25">
-        <f>AC$11</f>
+      <c r="BP4" s="23">
+        <f t="shared" si="2"/>
         <v>17989</v>
       </c>
-      <c r="BQ4" s="25">
-        <f>AD$11</f>
+      <c r="BQ4" s="23">
+        <f t="shared" si="2"/>
         <v>19199</v>
       </c>
-      <c r="BR4" s="25">
-        <f>AE$11</f>
+      <c r="BR4" s="23">
+        <f t="shared" si="2"/>
         <v>21788.5</v>
       </c>
-      <c r="BS4" s="25">
-        <f>AF$11</f>
+      <c r="BS4" s="23">
+        <f t="shared" si="2"/>
         <v>23221</v>
       </c>
-      <c r="BT4" s="25">
-        <f>AG$11</f>
+      <c r="BT4" s="23">
+        <f t="shared" si="2"/>
         <v>25072</v>
       </c>
-      <c r="BU4" s="25">
-        <f>AH$11</f>
+      <c r="BU4" s="23">
+        <f t="shared" si="2"/>
         <v>26966</v>
       </c>
     </row>
@@ -19232,11 +19235,11 @@
         <f>K5*1.4</f>
         <v>266000</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="M5" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
       <c r="T5" s="7" t="s">
         <v>34</v>
       </c>
@@ -19257,35 +19260,35 @@
         <v>0.13219197305641314</v>
       </c>
       <c r="Z5" s="9">
-        <f t="shared" ref="Z5" si="1">(Z10-V10)/V10</f>
+        <f t="shared" ref="Z5" si="3">(Z10-V10)/V10</f>
         <v>0.17247354125690736</v>
       </c>
       <c r="AA5" s="9">
-        <f t="shared" ref="AA5" si="2">(AA10-W10)/W10</f>
+        <f t="shared" ref="AA5" si="4">(AA10-W10)/W10</f>
         <v>0.18703703703703703</v>
       </c>
       <c r="AB5" s="9">
-        <f t="shared" ref="AB5" si="3">(AB10-X10)/X10</f>
+        <f t="shared" ref="AB5" si="5">(AB10-X10)/X10</f>
         <v>0.1905112971074201</v>
       </c>
       <c r="AC5" s="9">
-        <f t="shared" ref="AC5" si="4">(AC10-Y10)/Y10</f>
+        <f t="shared" ref="AC5" si="6">(AC10-Y10)/Y10</f>
         <v>0.189307552470666</v>
       </c>
       <c r="AD5" s="9">
-        <f t="shared" ref="AD5" si="5">(AD10-Z10)/Z10</f>
+        <f t="shared" ref="AD5" si="7">(AD10-Z10)/Z10</f>
         <v>0.16894995406797939</v>
       </c>
       <c r="AE5" s="9">
-        <f t="shared" ref="AE5" si="6">(AE10-AA10)/AA10</f>
+        <f t="shared" ref="AE5" si="8">(AE10-AA10)/AA10</f>
         <v>0.17472698907956319</v>
       </c>
       <c r="AF5" s="9">
-        <f t="shared" ref="AF5" si="7">(AF10-AB10)/AB10</f>
+        <f t="shared" ref="AF5" si="9">(AF10-AB10)/AB10</f>
         <v>0.20231677109135945</v>
       </c>
       <c r="AG5" s="9">
-        <f t="shared" ref="AG5" si="8">(AG10-AC10)/AC10</f>
+        <f t="shared" ref="AG5" si="10">(AG10-AC10)/AC10</f>
         <v>0.23598276940179252</v>
       </c>
       <c r="AH5" s="9">
@@ -19348,35 +19351,35 @@
         <f t="shared" si="0"/>
         <v>0.63360522022838495</v>
       </c>
-      <c r="BN5" s="24" t="s">
+      <c r="BN5" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="BO5" s="25">
-        <f>AB$12</f>
+      <c r="BO5" s="23">
+        <f t="shared" ref="BO5:BU5" si="11">AB$12</f>
         <v>11353</v>
       </c>
-      <c r="BP5" s="25">
-        <f>AC$12</f>
+      <c r="BP5" s="23">
+        <f t="shared" si="11"/>
         <v>11955</v>
       </c>
-      <c r="BQ5" s="25">
-        <f>AD$12</f>
+      <c r="BQ5" s="23">
+        <f t="shared" si="11"/>
         <v>12260</v>
       </c>
-      <c r="BR5" s="25">
-        <f>AE$12</f>
+      <c r="BR5" s="23">
+        <f t="shared" si="11"/>
         <v>13624</v>
       </c>
-      <c r="BS5" s="25">
-        <f>AF$12</f>
+      <c r="BS5" s="23">
+        <f t="shared" si="11"/>
         <v>15157</v>
       </c>
-      <c r="BT5" s="25">
-        <f>AG$12</f>
+      <c r="BT5" s="23">
+        <f t="shared" si="11"/>
         <v>17664</v>
       </c>
-      <c r="BU5" s="25">
-        <f>AH$12</f>
+      <c r="BU5" s="23">
+        <f t="shared" si="11"/>
         <v>20028</v>
       </c>
     </row>
@@ -19409,11 +19412,11 @@
         <f>K6*1.25</f>
         <v>175000</v>
       </c>
-      <c r="M6" s="22" t="s">
+      <c r="M6" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
       <c r="T6" s="7" t="s">
         <v>33</v>
       </c>
@@ -19464,27 +19467,27 @@
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
       <c r="E7" s="15">
-        <f t="shared" ref="E7:J7" si="9">SUM(E3:E6)</f>
+        <f t="shared" ref="E7:J7" si="12">SUM(E3:E6)</f>
         <v>87883</v>
       </c>
       <c r="F7" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>119225</v>
       </c>
       <c r="G7" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>145123</v>
       </c>
       <c r="H7" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>157273.1</v>
       </c>
       <c r="I7" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>246117.3</v>
       </c>
       <c r="J7" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>408318</v>
       </c>
       <c r="K7" s="13">
@@ -19495,11 +19498,11 @@
         <f>SUM(L3:L6)</f>
         <v>984585</v>
       </c>
-      <c r="M7" s="22" t="s">
+      <c r="M7" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
       <c r="T7" s="7" t="s">
         <v>35</v>
       </c>
@@ -19520,35 +19523,35 @@
         <v>0.25659603554340399</v>
       </c>
       <c r="Z7" s="9">
-        <f t="shared" ref="Z7:AG7" si="10">(Z12-V12)/V12</f>
+        <f t="shared" ref="Z7:AG7" si="13">(Z12-V12)/V12</f>
         <v>0.28441105446740006</v>
       </c>
       <c r="AA7" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.28838251774374302</v>
       </c>
       <c r="AB7" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.34978004993460943</v>
       </c>
       <c r="AC7" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.3005874673629243</v>
       </c>
       <c r="AD7" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.2805514936285774</v>
       </c>
       <c r="AE7" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.31671015753358461</v>
       </c>
       <c r="AF7" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.33506562142165064</v>
       </c>
       <c r="AG7" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>0.47754077791718946</v>
       </c>
       <c r="AH7" s="9">
@@ -19558,28 +19561,28 @@
     </row>
     <row r="8" spans="2:73" x14ac:dyDescent="0.3">
       <c r="K8" s="8"/>
-      <c r="BN8" s="26" t="s">
+      <c r="BN8" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="BO8" s="26" t="s">
+      <c r="BO8" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="BP8" s="26" t="s">
+      <c r="BP8" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="BQ8" s="26" t="s">
+      <c r="BQ8" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="BR8" s="26" t="s">
+      <c r="BR8" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BS8" s="26" t="s">
+      <c r="BS8" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BT8" s="26" t="s">
+      <c r="BT8" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="BU8" s="26" t="s">
+      <c r="BU8" s="24" t="s">
         <v>49</v>
       </c>
     </row>
@@ -19677,35 +19680,35 @@
       <c r="AK9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="BN9" s="24" t="s">
+      <c r="BN9" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="BO9" s="25">
-        <f>AB$10*AB$5/(1+AB$5)</f>
+      <c r="BO9" s="23">
+        <f t="shared" ref="BO9:BU9" si="14">AB$10*AB$5/(1+AB$5)</f>
         <v>4393</v>
       </c>
-      <c r="BP9" s="25">
-        <f>AC$10*AC$5/(1+AC$5)</f>
+      <c r="BP9" s="23">
+        <f t="shared" si="14"/>
         <v>4582</v>
       </c>
-      <c r="BQ9" s="25">
-        <f>AD$10*AD$5/(1+AD$5)</f>
+      <c r="BQ9" s="23">
+        <f t="shared" si="14"/>
         <v>4230</v>
       </c>
-      <c r="BR9" s="25">
-        <f>AE$10*AE$5/(1+AE$5)</f>
+      <c r="BR9" s="23">
+        <f t="shared" si="14"/>
         <v>4592</v>
       </c>
-      <c r="BS9" s="25">
-        <f>AF$10*AF$5/(1+AF$5)</f>
+      <c r="BS9" s="23">
+        <f t="shared" si="14"/>
         <v>5554</v>
       </c>
-      <c r="BT9" s="25">
-        <f>AG$10*AG$5/(1+AG$5)</f>
+      <c r="BT9" s="23">
+        <f t="shared" si="14"/>
         <v>6793</v>
       </c>
-      <c r="BU9" s="25">
-        <f>AH$10*AH$5/(1+AH$5)</f>
+      <c r="BU9" s="23">
+        <f t="shared" si="14"/>
         <v>8320</v>
       </c>
     </row>
@@ -19788,35 +19791,35 @@
       <c r="AH10" s="8">
         <v>37587</v>
       </c>
-      <c r="BN10" s="24" t="s">
+      <c r="BN10" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="BO10" s="25">
-        <f>AB$11*AB$6/(1+AB$6)</f>
+      <c r="BO10" s="23">
+        <f t="shared" ref="BO10:BU10" si="15">AB$11*AB$6/(1+AB$6)</f>
         <v>4082.8202975963372</v>
       </c>
-      <c r="BP10" s="25">
-        <f>AC$11*AC$6/(1+AC$6)</f>
+      <c r="BP10" s="23">
+        <f t="shared" si="15"/>
         <v>4256.93893129771</v>
       </c>
-      <c r="BQ10" s="25">
-        <f>AD$11*AD$6/(1+AD$6)</f>
+      <c r="BQ10" s="23">
+        <f t="shared" si="15"/>
         <v>4763.6616541353378</v>
       </c>
-      <c r="BR10" s="25">
-        <f>AE$11*AE$6/(1+AE$6)</f>
+      <c r="BR10" s="23">
+        <f t="shared" si="15"/>
         <v>6118.9566702624952</v>
       </c>
-      <c r="BS10" s="25">
-        <f>AF$11*AF$6/(1+AF$6)</f>
+      <c r="BS10" s="23">
+        <f t="shared" si="15"/>
         <v>6634.5714285714284</v>
       </c>
-      <c r="BT10" s="25">
-        <f>AG$11*AG$6/(1+AG$6)</f>
+      <c r="BT10" s="23">
+        <f t="shared" si="15"/>
         <v>7034.5899280575532</v>
       </c>
-      <c r="BU10" s="25">
-        <f>AH$11*AH$6/(1+AH$6)</f>
+      <c r="BU10" s="23">
+        <f t="shared" si="15"/>
         <v>7704.5714285714303</v>
       </c>
     </row>
@@ -19875,35 +19878,35 @@
       <c r="AH11" s="8">
         <v>26966</v>
       </c>
-      <c r="BN11" s="24" t="s">
+      <c r="BN11" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="BO11" s="25">
-        <f>AB$12*AB$7/(1+AB$7)</f>
+      <c r="BO11" s="23">
+        <f t="shared" ref="BO11:BU11" si="16">AB$12*AB$7/(1+AB$7)</f>
         <v>2942.0000000000005</v>
       </c>
-      <c r="BP11" s="25">
-        <f>AC$12*AC$7/(1+AC$7)</f>
+      <c r="BP11" s="23">
+        <f t="shared" si="16"/>
         <v>2763</v>
       </c>
-      <c r="BQ11" s="25">
-        <f>AD$12*AD$7/(1+AD$7)</f>
+      <c r="BQ11" s="23">
+        <f t="shared" si="16"/>
         <v>2686</v>
       </c>
-      <c r="BR11" s="25">
-        <f>AE$12*AE$7/(1+AE$7)</f>
+      <c r="BR11" s="23">
+        <f t="shared" si="16"/>
         <v>3277</v>
       </c>
-      <c r="BS11" s="25">
-        <f>AF$12*AF$7/(1+AF$7)</f>
+      <c r="BS11" s="23">
+        <f t="shared" si="16"/>
         <v>3803.9999999999995</v>
       </c>
-      <c r="BT11" s="25">
-        <f>AG$12*AG$7/(1+AG$7)</f>
+      <c r="BT11" s="23">
+        <f t="shared" si="16"/>
         <v>5709</v>
       </c>
-      <c r="BU11" s="25">
-        <f>AH$12*AH$7/(1+AH$7)</f>
+      <c r="BU11" s="23">
+        <f t="shared" si="16"/>
         <v>7768</v>
       </c>
     </row>
@@ -20020,31 +20023,31 @@
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="15">
-        <f t="shared" ref="E14:K14" si="11">SUM(E10:E13)</f>
+        <f t="shared" ref="E14:K14" si="17">SUM(E10:E13)</f>
         <v>230610</v>
       </c>
       <c r="F14" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>272402</v>
       </c>
       <c r="G14" s="15">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>277757</v>
       </c>
       <c r="H14" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>345387</v>
       </c>
       <c r="I14" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>451052</v>
       </c>
       <c r="J14" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>559329</v>
       </c>
       <c r="K14" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>678552</v>
       </c>
     </row>
@@ -20084,31 +20087,31 @@
         <v>2</v>
       </c>
       <c r="E17" s="16">
-        <f t="shared" ref="E17:K20" si="12">E3/E10</f>
+        <f t="shared" ref="E17:K20" si="18">E3/E10</f>
         <v>0.53048558973116977</v>
       </c>
       <c r="F17" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1.1957605715889221</v>
       </c>
       <c r="G17" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1.2474546543463381</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.62829326866479884</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.72363799546070406</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.94445301218332467</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1.178030552085388</v>
       </c>
     </row>
@@ -20117,31 +20120,31 @@
         <v>4</v>
       </c>
       <c r="E18" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.25448702101359705</v>
       </c>
       <c r="F18" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.26872556684910087</v>
       </c>
       <c r="G18" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.26827652046947831</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.5003436779246877</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.60870111684718431</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.79548625901499681</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1.1355233377585692</v>
       </c>
     </row>
@@ -20150,31 +20153,31 @@
         <v>5</v>
       </c>
       <c r="E19" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.34213193292795285</v>
       </c>
       <c r="F19" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.26884301488238116</v>
       </c>
       <c r="G19" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.34411716487239741</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.32251882137872739</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.42177511392748546</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.5649402293686594</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.97547451701176213</v>
       </c>
     </row>
@@ -20183,31 +20186,31 @@
         <v>6</v>
       </c>
       <c r="E20" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.3900947170103492</v>
       </c>
       <c r="F20" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.32187992996203385</v>
       </c>
       <c r="G20" s="16">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.62270430906389307</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.38341794046095651</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.40793622985283812</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>0.62366148531951637</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>1.0746250326225457</v>
       </c>
     </row>
@@ -20218,27 +20221,27 @@
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
       <c r="E21" s="17">
-        <f t="shared" ref="E21" si="13">SUM(E17:E20)</f>
+        <f t="shared" ref="E21" si="19">SUM(E17:E20)</f>
         <v>1.5171992606830689</v>
       </c>
       <c r="F21" s="17">
-        <f t="shared" ref="F21" si="14">SUM(F17:F20)</f>
+        <f t="shared" ref="F21" si="20">SUM(F17:F20)</f>
         <v>2.0552090832824383</v>
       </c>
       <c r="G21" s="17">
-        <f t="shared" ref="G21" si="15">SUM(G17:G20)</f>
+        <f t="shared" ref="G21" si="21">SUM(G17:G20)</f>
         <v>2.4825526487521072</v>
       </c>
       <c r="H21" s="18">
-        <f t="shared" ref="H21" si="16">SUM(H17:H20)</f>
+        <f t="shared" ref="H21" si="22">SUM(H17:H20)</f>
         <v>1.8345737084291704</v>
       </c>
       <c r="I21" s="18">
-        <f t="shared" ref="I21" si="17">SUM(I17:I20)</f>
+        <f t="shared" ref="I21" si="23">SUM(I17:I20)</f>
         <v>2.1620504560882119</v>
       </c>
       <c r="J21" s="18">
-        <f t="shared" ref="J21" si="18">SUM(J17:J20)</f>
+        <f t="shared" ref="J21" si="24">SUM(J17:J20)</f>
         <v>2.9285409858864972</v>
       </c>
       <c r="K21" s="18">
